--- a/data/encounters/suspected_mortality_updated.xlsx
+++ b/data/encounters/suspected_mortality_updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarcusMichelangeli\GIT projects\Git_repo\drugged_lakes_griffith_repo\drugged_lakes\data\encounters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F166B1C-A430-467B-92DA-6EA101A83200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9613365D-E010-4CC7-A13D-9EA8F6C87E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="89">
   <si>
     <t>individual_ID</t>
   </si>
@@ -115,9 +115,6 @@
     <t>likely_predated</t>
   </si>
   <si>
-    <t>mortality</t>
-  </si>
-  <si>
     <t>muddyfoot</t>
   </si>
   <si>
@@ -241,9 +238,6 @@
     <t>F59878</t>
   </si>
   <si>
-    <t>Very poor tracking. Maybe dead on 13/10/2022. Remove due to poor tracking.</t>
-  </si>
-  <si>
     <t>Maybe dead on 27/10/2022</t>
   </si>
   <si>
@@ -253,9 +247,6 @@
     <t>Unclear.</t>
   </si>
   <si>
-    <t>Poor tracking. Remove</t>
-  </si>
-  <si>
     <t>Maybe dead on 20/10/2022. Movement changes dramatically</t>
   </si>
   <si>
@@ -281,6 +272,24 @@
   </si>
   <si>
     <t>28/09/2022 to 03/10/2022</t>
+  </si>
+  <si>
+    <t>Very poor tracking. REMOVED</t>
+  </si>
+  <si>
+    <t>Poor tracking. REMOVED</t>
+  </si>
+  <si>
+    <t>F59898</t>
+  </si>
+  <si>
+    <t>F59896</t>
+  </si>
+  <si>
+    <t>F59895</t>
+  </si>
+  <si>
+    <t>REMOVE POOR TRACKING</t>
   </si>
 </sst>
 </file>
@@ -343,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -352,6 +361,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -652,7 +662,7 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -672,27 +682,27 @@
         <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>14</v>
@@ -701,15 +711,15 @@
         <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
@@ -718,15 +728,15 @@
         <v>44834</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>14</v>
@@ -735,15 +745,15 @@
         <v>44840</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>2</v>
@@ -752,15 +762,15 @@
         <v>44829</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>14</v>
@@ -769,15 +779,15 @@
         <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>14</v>
@@ -789,15 +799,15 @@
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>14</v>
@@ -810,10 +820,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>2</v>
@@ -822,18 +832,18 @@
         <v>44847</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>2</v>
@@ -844,10 +854,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>14</v>
@@ -859,18 +869,18 @@
         <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>2</v>
@@ -879,18 +889,18 @@
         <v>44842</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>14</v>
@@ -899,21 +909,21 @@
         <v>44834</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>2</v>
@@ -922,18 +932,18 @@
         <v>44852</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2</v>
@@ -942,18 +952,18 @@
         <v>44829</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>14</v>
@@ -964,10 +974,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>2</v>
@@ -976,18 +986,18 @@
         <v>44850</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2</v>
@@ -996,15 +1006,15 @@
         <v>26</v>
       </c>
       <c r="H18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>2</v>
@@ -1013,7 +1023,7 @@
         <v>44833</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1044,7 +1054,7 @@
         <v>44841</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1075,7 +1085,7 @@
         <v>44836</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1124,7 +1134,7 @@
         <v>44839</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1155,7 +1165,7 @@
         <v>44842</v>
       </c>
       <c r="E28" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1186,7 +1196,7 @@
         <v>44852</v>
       </c>
       <c r="E30" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1217,7 +1227,7 @@
         <v>44836</v>
       </c>
       <c r="E32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F32" t="s">
         <v>15</v>
@@ -1237,7 +1247,7 @@
         <v>44842</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
         <v>3</v>
@@ -1257,7 +1267,7 @@
         <v>44852</v>
       </c>
       <c r="E34" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1274,7 +1284,7 @@
         <v>44836</v>
       </c>
       <c r="E35" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F35" t="s">
         <v>3</v>
@@ -1308,12 +1318,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
@@ -1322,52 +1332,55 @@
         <v>44854</v>
       </c>
       <c r="E38" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>61</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="2">
+        <v>44859</v>
+      </c>
+      <c r="E40" t="s">
+        <v>79</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>62</v>
       </c>
-      <c r="B40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>63</v>
-      </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
@@ -1378,13 +1391,16 @@
       <c r="E41" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F41" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
@@ -1393,67 +1409,75 @@
         <v>44853</v>
       </c>
       <c r="E42" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="F42" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="2">
+        <v>44855</v>
+      </c>
+      <c r="E43" t="s">
+        <v>79</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>65</v>
       </c>
-      <c r="B43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" t="s">
-        <v>26</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="2">
+        <v>44845</v>
+      </c>
+      <c r="E44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>66</v>
       </c>
-      <c r="B44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" s="2">
-        <v>44844</v>
-      </c>
-      <c r="E44" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="2">
+        <v>44861</v>
+      </c>
+      <c r="E45" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>67</v>
       </c>
-      <c r="B45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="2">
-        <v>44844</v>
-      </c>
-      <c r="E45" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>68</v>
-      </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -1462,61 +1486,64 @@
         <v>44854</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="H46" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="8">
+        <v>44831</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="H47" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B47" t="s">
-        <v>59</v>
-      </c>
-      <c r="C47" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" s="2">
-        <v>44836</v>
-      </c>
-      <c r="E47" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="B48" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>70</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>71</v>
-      </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="2">
-        <v>44844</v>
+        <v>44807</v>
       </c>
       <c r="E49" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">

--- a/data/encounters/suspected_mortality_updated.xlsx
+++ b/data/encounters/suspected_mortality_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarcusMichelangeli\GIT projects\Git_repo\drugged_lakes_griffith_repo\drugged_lakes\data\encounters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarcusMichelangeli\Documents\Git_repo\drugged_lakes_griffith_repo\drugged_lakes\data\encounters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9613365D-E010-4CC7-A13D-9EA8F6C87E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52987502-E3D1-4DE2-A3D3-EAF569A6F896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -661,11 +661,11 @@
   <dimension ref="A1:H54"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.28515625" customWidth="1"/>
     <col min="7" max="7" width="38.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="52.42578125" bestFit="1" customWidth="1"/>

--- a/data/encounters/suspected_mortality_updated.xlsx
+++ b/data/encounters/suspected_mortality_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarcusMichelangeli\Documents\Git_repo\drugged_lakes_griffith_repo\drugged_lakes\data\encounters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52987502-E3D1-4DE2-A3D3-EAF569A6F896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864A6D53-78C0-42D2-835A-16734D3937A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31140" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="88">
   <si>
     <t>individual_ID</t>
   </si>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>revised_suspected_mortality</t>
-  </si>
-  <si>
-    <t>likely_predated</t>
   </si>
   <si>
     <t>muddyfoot</t>
@@ -682,27 +679,27 @@
         <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>14</v>
@@ -711,15 +708,15 @@
         <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
@@ -728,15 +725,15 @@
         <v>44834</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>14</v>
@@ -745,15 +742,15 @@
         <v>44840</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>2</v>
@@ -762,15 +759,15 @@
         <v>44829</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>14</v>
@@ -779,15 +776,15 @@
         <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>14</v>
@@ -799,15 +796,15 @@
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>14</v>
@@ -820,10 +817,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>2</v>
@@ -832,18 +829,18 @@
         <v>44847</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>2</v>
@@ -854,10 +851,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>14</v>
@@ -866,21 +863,21 @@
         <v>44832</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>2</v>
@@ -889,18 +886,18 @@
         <v>44842</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>14</v>
@@ -909,21 +906,21 @@
         <v>44834</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>2</v>
@@ -932,18 +929,18 @@
         <v>44852</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2</v>
@@ -952,18 +949,18 @@
         <v>44829</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>14</v>
@@ -974,10 +971,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>2</v>
@@ -986,18 +983,18 @@
         <v>44850</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2</v>
@@ -1006,15 +1003,15 @@
         <v>26</v>
       </c>
       <c r="H18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>2</v>
@@ -1023,7 +1020,7 @@
         <v>44833</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1054,7 +1051,7 @@
         <v>44841</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1085,7 +1082,7 @@
         <v>44836</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1134,7 +1131,7 @@
         <v>44839</v>
       </c>
       <c r="E26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1165,7 +1162,7 @@
         <v>44842</v>
       </c>
       <c r="E28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1196,7 +1193,7 @@
         <v>44852</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1227,7 +1224,7 @@
         <v>44836</v>
       </c>
       <c r="E32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s">
         <v>15</v>
@@ -1247,7 +1244,7 @@
         <v>44842</v>
       </c>
       <c r="E33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s">
         <v>3</v>
@@ -1267,7 +1264,7 @@
         <v>44852</v>
       </c>
       <c r="E34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1284,7 +1281,7 @@
         <v>44836</v>
       </c>
       <c r="E35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F35" t="s">
         <v>3</v>
@@ -1320,10 +1317,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
@@ -1332,35 +1329,35 @@
         <v>44854</v>
       </c>
       <c r="E38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" t="s">
         <v>2</v>
@@ -1369,18 +1366,18 @@
         <v>44859</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
@@ -1392,15 +1389,15 @@
         <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
@@ -1409,18 +1406,18 @@
         <v>44853</v>
       </c>
       <c r="E42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C43" t="s">
         <v>2</v>
@@ -1429,18 +1426,18 @@
         <v>44855</v>
       </c>
       <c r="E43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -1449,15 +1446,15 @@
         <v>44845</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -1466,18 +1463,18 @@
         <v>44861</v>
       </c>
       <c r="E45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -1486,18 +1483,18 @@
         <v>44854</v>
       </c>
       <c r="E46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>14</v>
@@ -1506,35 +1503,35 @@
         <v>44831</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
@@ -1543,7 +1540,7 @@
         <v>44807</v>
       </c>
       <c r="E49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
